--- a/human_resources_surveys/016_team_building_preference_survey--human_resources_surveys.xlsx
+++ b/human_resources_surveys/016_team_building_preference_survey--human_resources_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -531,24 +531,24 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>availability</t>
+          <t>available_time</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Availability</t>
+          <t>Available Time</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,24 +561,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>available_time</t>
+          <t>employee_feedback</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Available Time</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8-5 or 8-12</t>
-        </is>
-      </c>
+          <t>Employee Feedback</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -588,69 +584,69 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Feedback</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>team_activities</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Team Activities</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -662,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>employee_feedback</t>
+          <t>team_leadership</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Employee Feedback</t>
+          <t>Team Leadership</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -685,409 +681,87 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>team_activities</t>
+          <t>preferred_leadership</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Team Activities</t>
+          <t>Preferred Leadership</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>preferred_time</t>
+          <t>team_activities_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Preferred Time</t>
+          <t>Team Activities 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>team_leadership</t>
+          <t>team_leadership_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Team Leadership</t>
+          <t>Team Leadership 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>team_leadership_2</t>
+          <t>preferred_leadership_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Team Leadership</t>
+          <t>Preferred Leadership 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>team_leadership_3</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Team Leadership</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>team_leadership_4</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Team Leadership</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>preferred_leadership</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Preferred Leadership</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>feedback_2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Feedback 2</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>team_activities_2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Team Activities 2</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>team_leadership_5</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Team Leadership</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>team_leadership_6</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Team Leadership</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>team_leadership_7</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Team Leadership</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>team_leadership_8</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Team Leadership</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>team_leadership_9</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Team Leadership</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>team_leadership_10</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Team Leadership</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>preferred_leadership_2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Preferred Leadership 2</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>preferred_leadership_3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Preferred Leadership</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>team_leadership_11</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Team Leadership</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1102,12 +776,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1130,221 +804,221 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>employee_feedback_choices</t>
+          <t>employee_preferences_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>team_activities</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Team Activities</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>employee_feedback_choices</t>
+          <t>employee_preferences_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>team_building</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Team Building</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>employee_feedback_choices</t>
+          <t>employee_preferences_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>team_meetings</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Team Meetings</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>team_activities_choices</t>
+          <t>feedback_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>team_activities_choices</t>
+          <t>feedback_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>team_leadership_choices</t>
+          <t>feedback_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>team_leadership_choices</t>
+          <t>team_activities_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>team_leadership_2_choices</t>
+          <t>team_activities_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>team_leadership_2_choices</t>
+          <t>team_leadership_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>approachable</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Approachable</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>team_leadership_3_choices</t>
+          <t>team_leadership_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>supportive</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Supportive</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>team_leadership_3_choices</t>
+          <t>team_leadership_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>experienced</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>team_leadership_4_choices</t>
+          <t>team_leadership_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>knowledgeable</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Knowledgeable</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>team_leadership_4_choices</t>
+          <t>team_leadership_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1030,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>approachable</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Approachable</t>
         </is>
       </c>
     </row>
@@ -1373,352 +1047,250 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>supportive</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Supportive</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>team_activities_2_choices</t>
+          <t>preferred_leadership_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>experienced</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>team_activities_2_choices</t>
+          <t>preferred_leadership_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>knowledgeable</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Knowledgeable</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>team_leadership_5_choices</t>
+          <t>preferred_leadership_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>team_leadership_5_choices</t>
+          <t>team_activities_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>team_leadership_6_choices</t>
+          <t>team_activities_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>team_leadership_6_choices</t>
+          <t>team_leadership_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>supportive</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Supportive</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>team_leadership_7_choices</t>
+          <t>team_leadership_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>experienced</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>team_leadership_7_choices</t>
+          <t>team_leadership_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>knowledgeable</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Knowledgeable</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>team_leadership_8_choices</t>
+          <t>team_leadership_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>team_leadership_8_choices</t>
+          <t>preferred_leadership_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>approachable</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Approachable</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>team_leadership_9_choices</t>
+          <t>preferred_leadership_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>supportive</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Supportive</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>team_leadership_9_choices</t>
+          <t>preferred_leadership_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>experienced</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Experienced</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>team_leadership_10_choices</t>
+          <t>preferred_leadership_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>knowledgeable</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Knowledgeable</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>team_leadership_10_choices</t>
+          <t>preferred_leadership_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>preferred_leadership_2_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>preferred_leadership_2_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>preferred_leadership_3_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>preferred_leadership_3_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>team_leadership_11_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>team_leadership_11_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
